--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,24 +448,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>La mujer zorro y el doctor Shimamura</t>
+          <t>Fin de viaje</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Christine Wunnicke</t>
+          <t>Virginia Woolf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Impedimenta</t>
+          <t>Lumen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fin de viaje</t>
+          <t>Noche y día</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Noche y día</t>
+          <t>El cuarto de Jacob</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>El cuarto de Jacob</t>
+          <t>Al faro</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Al faro</t>
+          <t>Los años</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -533,24 +533,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Los años</t>
+          <t>El plan infinito</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Virginia Woolf</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Lumen</t>
-        </is>
-      </c>
+          <t>Isabel Allende</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>El plan infinito</t>
+          <t>La ciudad de las bestias</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -563,7 +559,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La ciudad de las bestias</t>
+          <t>El reino del dragón de oro</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -576,12 +572,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El reino del dragón de oro</t>
+          <t>El peso del corazón</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Isabel Allende</t>
+          <t>Rosa Montero</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -589,7 +585,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El peso del corazón</t>
+          <t>La ridicula idea de no volverte a ver</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -602,12 +598,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>La ridicula idea de no volverte a ver</t>
+          <t>El jardín de los Finzi Contini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rosa Montero</t>
+          <t>Giorgio Bassani</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -615,12 +611,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>El jardín de los Finzi Contini</t>
+          <t>Mañana no le presentes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Giorgio Bassani</t>
+          <t>Marta Orrantia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -628,12 +624,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mañana no le presentes</t>
+          <t>Primera persona</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Marta Orrantia</t>
+          <t>Margarita García Robayo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -641,12 +637,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Primera persona</t>
+          <t>Arráncame la vida</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Margarita García Robayo</t>
+          <t>Angeles Mastretta</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -654,12 +650,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Arráncame la vida</t>
+          <t>La mujer de mi vida</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Angeles Mastretta</t>
+          <t>Carla Guelfenbein</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -667,12 +663,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La mujer de mi vida</t>
+          <t>Memoria por correspondencia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carla Guelfenbein</t>
+          <t>Emma Reyes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -680,12 +676,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Memoria por correspondencia</t>
+          <t>Nombres y animales</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Emma Reyes</t>
+          <t>Rita Indiana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -693,12 +689,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nombres y animales</t>
+          <t>Diez lunas para una espera</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rita Indiana</t>
+          <t>Velia Vidal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -706,28 +702,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Diez lunas para una espera</t>
+          <t>La dependienta</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Velia Vidal</t>
+          <t>Sayaka Murata</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>La dependienta</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Sayaka Murata</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -773,54 +773,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Matar a un ruiseñor</t>
+          <t>La M de las moscas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harper Lee</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Lumen</t>
-        </is>
-      </c>
+          <t>Helena Araújo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>La M de las moscas</t>
+          <t>Siddhartha</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Helena Araújo</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>Herman Hesse</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Debolsillo Edición Especial en Tapa Dura</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Siddhartha</t>
+          <t>Afrodita</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Herman Hesse</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Debolsillo Edición Especial en Tapa Dura</t>
-        </is>
-      </c>
+          <t>Isabel Allende</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Afrodita</t>
+          <t xml:space="preserve">Amor </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -833,7 +829,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amor </t>
+          <t>Cuentos de Eva Luna</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -846,7 +842,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cuentos de Eva Luna</t>
+          <t>El juego de Ripper</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -859,7 +855,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>El juego de Ripper</t>
+          <t>El plan infinito</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -872,7 +868,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>El plan infinito</t>
+          <t>El viento conoce mi nombre</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -885,7 +881,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>El viento conoce mi nombre</t>
+          <t>El Zorro: comienza la leyenda</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -898,7 +894,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>El Zorro: comienza la leyenda</t>
+          <t>Inés del alma mía</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -911,7 +907,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Inés del alma mía</t>
+          <t>La gorda de porcelana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -924,7 +920,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>La gorda de porcelana</t>
+          <t>Largo pétalo de mar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -937,7 +933,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Largo pétalo de mar</t>
+          <t>Los amantes del Guggenheim</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -950,7 +946,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Los amantes del Guggenheim</t>
+          <t>Mi país inventado</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -963,7 +959,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mi país inventado</t>
+          <t>Mujeres del alma mía</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -976,7 +972,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mujeres del alma mía</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -989,12 +985,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>El señor de los anillos</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Isabel Allende</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1002,12 +998,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>El señor de los anillos</t>
+          <t>Juvenilia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Jane Austen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1015,12 +1011,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Juvenilia</t>
+          <t>El principio del mundo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jane Austen</t>
+          <t>Jeremías Gamboa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1028,12 +1024,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>El principio del mundo</t>
+          <t>Los viejos marineros</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jeremías Gamboa</t>
+          <t>Jorge Amador</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1041,25 +1037,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Los viejos marineros</t>
+          <t>El Aleph</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jorge Amador</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Jorge Luis Borges</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Debolsillo Edición Especial en Tapa Dura</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>El Aleph</t>
+          <t>Ensayo sobre la ceguera</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jorge Luis Borges</t>
+          <t>José Saramago</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1071,29 +1071,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ensayo sobre la ceguera</t>
+          <t>Tú no matarás</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>José Saramago</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Debolsillo Edición Especial en Tapa Dura</t>
-        </is>
-      </c>
+          <t>Julia Navarro</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tú no matarás</t>
+          <t>Pan piedra</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Julia Navarro</t>
+          <t>Laura Andrea Garzón</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1101,12 +1097,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pan piedra</t>
+          <t>Delirio</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Laura Andrea Garzón</t>
+          <t>Laura Restrepo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1114,7 +1110,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Delirio</t>
+          <t>Los Divinos</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1127,12 +1123,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Los Divinos</t>
+          <t>Una noche en el paraíso</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Laura Restrepo</t>
+          <t>Lucía Berlín</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1140,12 +1136,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Una noche en el paraíso</t>
+          <t>Las amazonas: mito e historia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lucía Berlín</t>
+          <t>Lyn Webster Wild</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1153,12 +1149,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Las amazonas: mito e historia</t>
+          <t>Hamnet</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lyn Webster Wild</t>
+          <t>Maggie O'Farrell</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1166,12 +1162,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hamnet</t>
+          <t>Chambacú, corral de negros</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Maggie O'Farrell</t>
+          <t>Manuel Zapata Olivella</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1179,7 +1175,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Chambacú, corral de negros</t>
+          <t>Changó, el gran putas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1192,7 +1188,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Changó, el gran putas</t>
+          <t>En Chimá nace un santo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1205,12 +1201,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>En Chimá nace un santo</t>
+          <t>El sonido de las olas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Manuel Zapata Olivella</t>
+          <t>Margarita García Robayo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1218,7 +1214,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>El sonido de las olas</t>
+          <t>Primera persona</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1231,12 +1227,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Primera persona</t>
+          <t>Al otro lado del Mar</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Margarita García Robayo</t>
+          <t>María Cristina Restrepo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1244,12 +1240,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Al otro lado del Mar</t>
+          <t>Lais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>María Cristina Restrepo</t>
+          <t>María de Francia</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1257,12 +1253,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Lais</t>
+          <t>Cartas a un joven sicólogo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>María de Francia</t>
+          <t>María Dolores Avia</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1270,12 +1266,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cartas a un joven sicólogo</t>
+          <t>Los nombres que olvidamos</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>María Dolores Avia</t>
+          <t>María F. Fitzgerald</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1283,12 +1279,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Los nombres que olvidamos</t>
+          <t>Solo un poco aquí</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>María F. Fitzgerald</t>
+          <t>María Ospina Pizano</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1296,12 +1292,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solo un poco aquí</t>
+          <t>Este es el mar</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>María Ospina Pizano</t>
+          <t>Mariana Enriquez</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1309,12 +1305,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Este es el mar</t>
+          <t>Niñapájaroglaciar</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mariana Enriquez</t>
+          <t>Mariana Matija</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1322,12 +1318,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Niñapájaroglaciar</t>
+          <t>Mañana no te presentes</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mariana Matija</t>
+          <t>Marta Orrantia</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1335,12 +1331,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mañana no te presentes</t>
+          <t>Cuentos</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Marta Orrantia</t>
+          <t>Marvel Moreno</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1348,7 +1344,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cuentos</t>
+          <t>En diciembre llegaban las garzas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1361,12 +1357,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>En diciembre llegaban las garzas</t>
+          <t>La casa de la belleza</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Marvel Moreno</t>
+          <t>Melba Escobar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1374,12 +1370,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>La casa de la belleza</t>
+          <t>Reinventar el amor</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Melba Escobar</t>
+          <t>Mona Chollet</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1387,12 +1383,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Reinventar el amor</t>
+          <t>El enigma del amuleto</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mona Chollet</t>
+          <t>Mónica Acebedo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1400,12 +1396,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>El enigma del amuleto</t>
+          <t>Los errantes</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mónica Acebedo</t>
+          <t>Olga Tokarczuk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1413,12 +1409,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Los errantes</t>
+          <t>La mujer del pelo rojo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Olga Tokarczuk</t>
+          <t>Orhan Pamuk</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1426,12 +1422,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>La mujer del pelo rojo</t>
+          <t>Lo que no tiene nombre</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Orhan Pamuk</t>
+          <t>Piedad Bonnet</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1439,12 +1435,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lo que no tiene nombre</t>
+          <t>Diccionario</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Piedad Bonnet</t>
+          <t>RAE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1452,12 +1448,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Diccionario</t>
+          <t>Horizontes para la paz</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RAE</t>
+          <t>Rafael Pardo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1465,12 +1461,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Horizontes para la paz</t>
+          <t>Lola Vendetta: Katanazo al amor romántico</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rafael Pardo</t>
+          <t>Raquel Riba Rossy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1478,12 +1474,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Lola Vendetta: Katanazo al amor romántico</t>
+          <t>Nombres y animales</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Raquel Riba Rossy</t>
+          <t>Rita Indiana</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1491,12 +1487,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Nombres y animales</t>
+          <t>El peso del corazón</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rita Indiana</t>
+          <t>Rosa Montero</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1504,7 +1500,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>El peso del corazón</t>
+          <t>La ridícula idea de no volverte a ver</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1517,12 +1513,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>La ridícula idea de no volverte a ver</t>
+          <t>El crisantemo y la espada</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Rosa Montero</t>
+          <t>Ruth Benedict</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1530,12 +1526,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>El crisantemo y la espada</t>
+          <t>Pájaros en la Boca</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ruth Benedict</t>
+          <t>Samanta Schweblin</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1543,12 +1539,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pájaros en la Boca</t>
+          <t>La dependienta</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Samanta Schweblin</t>
+          <t>Sayaka Murata</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1556,12 +1552,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>La dependienta</t>
+          <t>Nada que decir</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sayaka Murata</t>
+          <t>Silvia Hidalgo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1569,12 +1565,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Nada que decir</t>
+          <t>La campana de cristal</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Silvia Hidalgo</t>
+          <t>Silvia Plath</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1582,12 +1578,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>La campana de cristal</t>
+          <t>Cauce y río</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Silvia Plath</t>
+          <t>Silvia Rivera Cusicanqui</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1595,42 +1591,42 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cauce y río</t>
+          <t>El mundo de ayer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Silvia Rivera Cusicanqui</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Stefan Zweig</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Alma</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>El mundo de ayer</t>
+          <t>Emily Dickinson y lo incompleto</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Stefan Zweig</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Alma</t>
-        </is>
-      </c>
+          <t>Tania Ganitsky</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Emily Dickinson y lo incompleto</t>
+          <t>The once and future king</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tania Ganitsky</t>
+          <t>TH White</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1638,12 +1634,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>The once and future king</t>
+          <t>Budismo para principiantes</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TH White</t>
+          <t>Thubten Chodron</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1651,12 +1647,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Budismo para principiantes</t>
+          <t>Cuántas veces nunca más</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Thubten Chodron</t>
+          <t>Valentina Upegui</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1664,12 +1660,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cuántas veces nunca más</t>
+          <t>Aguas de estuario</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Valentina Upegui</t>
+          <t>Velia Vidal</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1677,7 +1673,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Aguas de estuario</t>
+          <t>Diez lunas para una espera</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1690,20 +1686,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Diez lunas para una espera</t>
+          <t>Al faro</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Velia Vidal</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>Virginia Woolf</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Lumen</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Al faro</t>
+          <t>El cuarto de Jacob</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1720,7 +1720,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>El cuarto de Jacob</t>
+          <t>El lector común</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1737,7 +1737,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>El lector común</t>
+          <t>Fin de viaje</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1754,7 +1754,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Fin de viaje</t>
+          <t>Los años</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Los años</t>
+          <t>Momentos de vida</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Momentos de vida</t>
+          <t>Noche y día</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Noche y día</t>
+          <t>Tres guineas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Tres guineas</t>
+          <t>Una habitación propia</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1830,21 +1830,17 @@
           <t>Virginia Woolf</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Lumen</t>
-        </is>
-      </c>
+      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Una habitación propia</t>
+          <t>La casa de las bellas durmientes</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Virginia Woolf</t>
+          <t>Yasunari Kawabata</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1852,7 +1848,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>La casa de las bellas durmientes</t>
+          <t>Mil grullas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -1861,19 +1857,6 @@
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Mil grullas</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Yasunari Kawabata</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -1157,7 +1157,11 @@
           <t>Maggie O'Farrell</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Libros del Asteroide</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,24 +1149,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hamnet</t>
+          <t>Chambacú, corral de negros</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Maggie O'Farrell</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Libros del Asteroide</t>
-        </is>
-      </c>
+          <t>Manuel Zapata Olivella</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Chambacú, corral de negros</t>
+          <t>Changó, el gran putas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1179,7 +1175,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Changó, el gran putas</t>
+          <t>En Chimá nace un santo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1192,12 +1188,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>En Chimá nace un santo</t>
+          <t>El sonido de las olas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Manuel Zapata Olivella</t>
+          <t>Margarita García Robayo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1205,7 +1201,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>El sonido de las olas</t>
+          <t>Primera persona</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1218,12 +1214,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Primera persona</t>
+          <t>Al otro lado del Mar</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Margarita García Robayo</t>
+          <t>María Cristina Restrepo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1231,12 +1227,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Al otro lado del Mar</t>
+          <t>Lais</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>María Cristina Restrepo</t>
+          <t>María de Francia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1244,12 +1240,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lais</t>
+          <t>Cartas a un joven sicólogo</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>María de Francia</t>
+          <t>María Dolores Avia</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1257,12 +1253,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cartas a un joven sicólogo</t>
+          <t>Los nombres que olvidamos</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>María Dolores Avia</t>
+          <t>María F. Fitzgerald</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1270,12 +1266,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Los nombres que olvidamos</t>
+          <t>Solo un poco aquí</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>María F. Fitzgerald</t>
+          <t>María Ospina Pizano</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1283,12 +1279,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solo un poco aquí</t>
+          <t>Este es el mar</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>María Ospina Pizano</t>
+          <t>Mariana Enriquez</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1296,12 +1292,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Este es el mar</t>
+          <t>Niñapájaroglaciar</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mariana Enriquez</t>
+          <t>Mariana Matija</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1309,12 +1305,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Niñapájaroglaciar</t>
+          <t>Mañana no te presentes</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mariana Matija</t>
+          <t>Marta Orrantia</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1322,12 +1318,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mañana no te presentes</t>
+          <t>Cuentos</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marta Orrantia</t>
+          <t>Marvel Moreno</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1335,7 +1331,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cuentos</t>
+          <t>En diciembre llegaban las garzas</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1348,12 +1344,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>En diciembre llegaban las garzas</t>
+          <t>La casa de la belleza</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Marvel Moreno</t>
+          <t>Melba Escobar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1361,12 +1357,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>La casa de la belleza</t>
+          <t>Reinventar el amor</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Melba Escobar</t>
+          <t>Mona Chollet</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1374,12 +1370,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Reinventar el amor</t>
+          <t>El enigma del amuleto</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mona Chollet</t>
+          <t>Mónica Acebedo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1387,12 +1383,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>El enigma del amuleto</t>
+          <t>Los errantes</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mónica Acebedo</t>
+          <t>Olga Tokarczuk</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1400,12 +1396,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Los errantes</t>
+          <t>La mujer del pelo rojo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Olga Tokarczuk</t>
+          <t>Orhan Pamuk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1413,12 +1409,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>La mujer del pelo rojo</t>
+          <t>Lo que no tiene nombre</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Orhan Pamuk</t>
+          <t>Piedad Bonnet</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1426,12 +1422,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lo que no tiene nombre</t>
+          <t>Diccionario</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Piedad Bonnet</t>
+          <t>RAE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1439,12 +1435,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Diccionario</t>
+          <t>Horizontes para la paz</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RAE</t>
+          <t>Rafael Pardo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1452,12 +1448,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Horizontes para la paz</t>
+          <t>Lola Vendetta: Katanazo al amor romántico</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rafael Pardo</t>
+          <t>Raquel Riba Rossy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1465,12 +1461,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lola Vendetta: Katanazo al amor romántico</t>
+          <t>Nombres y animales</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Raquel Riba Rossy</t>
+          <t>Rita Indiana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1478,12 +1474,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Nombres y animales</t>
+          <t>El peso del corazón</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rita Indiana</t>
+          <t>Rosa Montero</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1491,7 +1487,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>El peso del corazón</t>
+          <t>La ridícula idea de no volverte a ver</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1504,12 +1500,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>La ridícula idea de no volverte a ver</t>
+          <t>El crisantemo y la espada</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rosa Montero</t>
+          <t>Ruth Benedict</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1517,12 +1513,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>El crisantemo y la espada</t>
+          <t>Pájaros en la Boca</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ruth Benedict</t>
+          <t>Samanta Schweblin</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1530,12 +1526,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Pájaros en la Boca</t>
+          <t>La dependienta</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Samanta Schweblin</t>
+          <t>Sayaka Murata</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1543,12 +1539,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>La dependienta</t>
+          <t>Nada que decir</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sayaka Murata</t>
+          <t>Silvia Hidalgo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1556,12 +1552,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nada que decir</t>
+          <t>La campana de cristal</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Silvia Hidalgo</t>
+          <t>Silvia Plath</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1569,12 +1565,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>La campana de cristal</t>
+          <t>Cauce y río</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Silvia Plath</t>
+          <t>Silvia Rivera Cusicanqui</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1582,42 +1578,42 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cauce y río</t>
+          <t>El mundo de ayer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Silvia Rivera Cusicanqui</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Stefan Zweig</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Alma</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>El mundo de ayer</t>
+          <t>Emily Dickinson y lo incompleto</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Stefan Zweig</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Alma</t>
-        </is>
-      </c>
+          <t>Tania Ganitsky</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Emily Dickinson y lo incompleto</t>
+          <t>The once and future king</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tania Ganitsky</t>
+          <t>TH White</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1625,12 +1621,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>The once and future king</t>
+          <t>Budismo para principiantes</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TH White</t>
+          <t>Thubten Chodron</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1638,12 +1634,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Budismo para principiantes</t>
+          <t>Cuántas veces nunca más</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Thubten Chodron</t>
+          <t>Valentina Upegui</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1651,12 +1647,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cuántas veces nunca más</t>
+          <t>Aguas de estuario</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Valentina Upegui</t>
+          <t>Velia Vidal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1664,7 +1660,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Aguas de estuario</t>
+          <t>Diez lunas para una espera</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1677,20 +1673,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Diez lunas para una espera</t>
+          <t>Al faro</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Velia Vidal</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>Virginia Woolf</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Lumen</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Al faro</t>
+          <t>El cuarto de Jacob</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>El cuarto de Jacob</t>
+          <t>El lector común</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1724,7 +1724,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>El lector común</t>
+          <t>Fin de viaje</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Fin de viaje</t>
+          <t>Los años</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Los años</t>
+          <t>Momentos de vida</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Momentos de vida</t>
+          <t>Noche y día</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Noche y día</t>
+          <t>Tres guineas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tres guineas</t>
+          <t>Una habitación propia</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1817,21 +1817,17 @@
           <t>Virginia Woolf</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Lumen</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Una habitación propia</t>
+          <t>La casa de las bellas durmientes</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Virginia Woolf</t>
+          <t>Yasunari Kawabata</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1839,7 +1835,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>La casa de las bellas durmientes</t>
+          <t>Mil grullas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -1848,19 +1844,6 @@
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Mil grullas</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Yasunari Kawabata</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1578,29 +1578,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>El mundo de ayer</t>
+          <t>Emily Dickinson y lo incompleto</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stefan Zweig</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Alma</t>
-        </is>
-      </c>
+          <t>Tania Ganitsky</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Emily Dickinson y lo incompleto</t>
+          <t>The once and future king</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tania Ganitsky</t>
+          <t>TH White</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1608,12 +1604,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>The once and future king</t>
+          <t>Budismo para principiantes</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TH White</t>
+          <t>Thubten Chodron</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1621,12 +1617,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Budismo para principiantes</t>
+          <t>Cuántas veces nunca más</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Thubten Chodron</t>
+          <t>Valentina Upegui</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1634,12 +1630,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cuántas veces nunca más</t>
+          <t>Aguas de estuario</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Valentina Upegui</t>
+          <t>Velia Vidal</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1647,7 +1643,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Aguas de estuario</t>
+          <t>Diez lunas para una espera</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1660,20 +1656,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Diez lunas para una espera</t>
+          <t>Al faro</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Velia Vidal</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>Virginia Woolf</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Lumen</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Al faro</t>
+          <t>El cuarto de Jacob</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1690,7 +1690,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>El cuarto de Jacob</t>
+          <t>El lector común</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>El lector común</t>
+          <t>Fin de viaje</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1724,7 +1724,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Fin de viaje</t>
+          <t>Los años</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Los años</t>
+          <t>Momentos de vida</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Momentos de vida</t>
+          <t>Noche y día</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Noche y día</t>
+          <t>Tres guineas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tres guineas</t>
+          <t>Una habitación propia</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1800,21 +1800,17 @@
           <t>Virginia Woolf</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Lumen</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Una habitación propia</t>
+          <t>La casa de las bellas durmientes</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Virginia Woolf</t>
+          <t>Yasunari Kawabata</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1822,7 +1818,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>La casa de las bellas durmientes</t>
+          <t>Mil grullas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1831,19 +1827,6 @@
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Mil grullas</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Yasunari Kawabata</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,24 +786,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Siddhartha</t>
+          <t>Afrodita</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Herman Hesse</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Debolsillo Edición Especial en Tapa Dura</t>
-        </is>
-      </c>
+          <t>Isabel Allende</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Afrodita</t>
+          <t xml:space="preserve">Amor </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -816,7 +812,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amor </t>
+          <t>Cuentos de Eva Luna</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -829,7 +825,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cuentos de Eva Luna</t>
+          <t>El juego de Ripper</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -842,7 +838,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>El juego de Ripper</t>
+          <t>El plan infinito</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -855,7 +851,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>El plan infinito</t>
+          <t>El viento conoce mi nombre</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -868,7 +864,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>El viento conoce mi nombre</t>
+          <t>El Zorro: comienza la leyenda</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -881,7 +877,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>El Zorro: comienza la leyenda</t>
+          <t>Inés del alma mía</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -894,7 +890,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Inés del alma mía</t>
+          <t>La gorda de porcelana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -907,7 +903,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>La gorda de porcelana</t>
+          <t>Largo pétalo de mar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -920,7 +916,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Largo pétalo de mar</t>
+          <t>Los amantes del Guggenheim</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -933,7 +929,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Los amantes del Guggenheim</t>
+          <t>Mi país inventado</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -946,7 +942,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mi país inventado</t>
+          <t>Mujeres del alma mía</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -959,7 +955,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mujeres del alma mía</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -972,12 +968,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>El señor de los anillos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Isabel Allende</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -985,12 +981,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>El señor de los anillos</t>
+          <t>Juvenilia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Jane Austen</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -998,12 +994,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Juvenilia</t>
+          <t>El principio del mundo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jane Austen</t>
+          <t>Jeremías Gamboa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1011,12 +1007,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>El principio del mundo</t>
+          <t>Los viejos marineros</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jeremías Gamboa</t>
+          <t>Jorge Amador</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1024,25 +1020,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Los viejos marineros</t>
+          <t>El Aleph</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jorge Amador</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Jorge Luis Borges</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Debolsillo Edición Especial en Tapa Dura</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>El Aleph</t>
+          <t>Ensayo sobre la ceguera</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jorge Luis Borges</t>
+          <t>José Saramago</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1054,29 +1054,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ensayo sobre la ceguera</t>
+          <t>Tú no matarás</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>José Saramago</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Debolsillo Edición Especial en Tapa Dura</t>
-        </is>
-      </c>
+          <t>Julia Navarro</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tú no matarás</t>
+          <t>Pan piedra</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Julia Navarro</t>
+          <t>Laura Andrea Garzón</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1084,12 +1080,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pan piedra</t>
+          <t>Delirio</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Laura Andrea Garzón</t>
+          <t>Laura Restrepo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1097,7 +1093,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Delirio</t>
+          <t>Los Divinos</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1110,12 +1106,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Los Divinos</t>
+          <t>Una noche en el paraíso</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Laura Restrepo</t>
+          <t>Lucía Berlín</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1123,12 +1119,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Una noche en el paraíso</t>
+          <t>Las amazonas: mito e historia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lucía Berlín</t>
+          <t>Lyn Webster Wild</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1136,12 +1132,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Las amazonas: mito e historia</t>
+          <t>Chambacú, corral de negros</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lyn Webster Wild</t>
+          <t>Manuel Zapata Olivella</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1149,7 +1145,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Chambacú, corral de negros</t>
+          <t>Changó, el gran putas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1162,7 +1158,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Changó, el gran putas</t>
+          <t>En Chimá nace un santo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1175,12 +1171,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>En Chimá nace un santo</t>
+          <t>El sonido de las olas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Manuel Zapata Olivella</t>
+          <t>Margarita García Robayo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1188,7 +1184,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>El sonido de las olas</t>
+          <t>Primera persona</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1201,12 +1197,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Primera persona</t>
+          <t>Al otro lado del Mar</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Margarita García Robayo</t>
+          <t>María Cristina Restrepo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1214,12 +1210,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Al otro lado del Mar</t>
+          <t>Lais</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>María Cristina Restrepo</t>
+          <t>María de Francia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1227,12 +1223,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Lais</t>
+          <t>Cartas a un joven sicólogo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>María de Francia</t>
+          <t>María Dolores Avia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1240,12 +1236,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cartas a un joven sicólogo</t>
+          <t>Los nombres que olvidamos</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>María Dolores Avia</t>
+          <t>María F. Fitzgerald</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1253,12 +1249,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Los nombres que olvidamos</t>
+          <t>Solo un poco aquí</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>María F. Fitzgerald</t>
+          <t>María Ospina Pizano</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1266,12 +1262,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solo un poco aquí</t>
+          <t>Este es el mar</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>María Ospina Pizano</t>
+          <t>Mariana Enriquez</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1279,12 +1275,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Este es el mar</t>
+          <t>Niñapájaroglaciar</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mariana Enriquez</t>
+          <t>Mariana Matija</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1292,12 +1288,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Niñapájaroglaciar</t>
+          <t>Mañana no te presentes</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mariana Matija</t>
+          <t>Marta Orrantia</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1305,12 +1301,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mañana no te presentes</t>
+          <t>Cuentos</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Marta Orrantia</t>
+          <t>Marvel Moreno</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1318,7 +1314,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cuentos</t>
+          <t>En diciembre llegaban las garzas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1331,12 +1327,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>En diciembre llegaban las garzas</t>
+          <t>La casa de la belleza</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Marvel Moreno</t>
+          <t>Melba Escobar</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1344,12 +1340,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>La casa de la belleza</t>
+          <t>Reinventar el amor</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Melba Escobar</t>
+          <t>Mona Chollet</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1357,12 +1353,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Reinventar el amor</t>
+          <t>El enigma del amuleto</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mona Chollet</t>
+          <t>Mónica Acebedo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1370,12 +1366,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>El enigma del amuleto</t>
+          <t>Los errantes</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mónica Acebedo</t>
+          <t>Olga Tokarczuk</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1383,12 +1379,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Los errantes</t>
+          <t>La mujer del pelo rojo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Olga Tokarczuk</t>
+          <t>Orhan Pamuk</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1396,12 +1392,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>La mujer del pelo rojo</t>
+          <t>Lo que no tiene nombre</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Orhan Pamuk</t>
+          <t>Piedad Bonnet</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1409,12 +1405,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lo que no tiene nombre</t>
+          <t>Diccionario</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Piedad Bonnet</t>
+          <t>RAE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1422,12 +1418,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Diccionario</t>
+          <t>Horizontes para la paz</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RAE</t>
+          <t>Rafael Pardo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1435,12 +1431,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Horizontes para la paz</t>
+          <t>Lola Vendetta: Katanazo al amor romántico</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Rafael Pardo</t>
+          <t>Raquel Riba Rossy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1448,12 +1444,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Lola Vendetta: Katanazo al amor romántico</t>
+          <t>Nombres y animales</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Raquel Riba Rossy</t>
+          <t>Rita Indiana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1461,12 +1457,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Nombres y animales</t>
+          <t>El peso del corazón</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rita Indiana</t>
+          <t>Rosa Montero</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1474,7 +1470,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>El peso del corazón</t>
+          <t>La ridícula idea de no volverte a ver</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1487,12 +1483,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>La ridícula idea de no volverte a ver</t>
+          <t>El crisantemo y la espada</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rosa Montero</t>
+          <t>Ruth Benedict</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1500,12 +1496,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>El crisantemo y la espada</t>
+          <t>Pájaros en la Boca</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ruth Benedict</t>
+          <t>Samanta Schweblin</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1513,12 +1509,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Pájaros en la Boca</t>
+          <t>La dependienta</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Samanta Schweblin</t>
+          <t>Sayaka Murata</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1526,12 +1522,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>La dependienta</t>
+          <t>Nada que decir</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sayaka Murata</t>
+          <t>Silvia Hidalgo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1539,12 +1535,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Nada que decir</t>
+          <t>La campana de cristal</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Silvia Hidalgo</t>
+          <t>Silvia Plath</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1552,12 +1548,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>La campana de cristal</t>
+          <t>Cauce y río</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Silvia Plath</t>
+          <t>Silvia Rivera Cusicanqui</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1565,12 +1561,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cauce y río</t>
+          <t>Emily Dickinson y lo incompleto</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Silvia Rivera Cusicanqui</t>
+          <t>Tania Ganitsky</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1578,12 +1574,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Emily Dickinson y lo incompleto</t>
+          <t>The once and future king</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tania Ganitsky</t>
+          <t>TH White</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1591,12 +1587,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>The once and future king</t>
+          <t>Budismo para principiantes</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TH White</t>
+          <t>Thubten Chodron</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1604,12 +1600,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Budismo para principiantes</t>
+          <t>Cuántas veces nunca más</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Thubten Chodron</t>
+          <t>Valentina Upegui</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1617,12 +1613,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cuántas veces nunca más</t>
+          <t>Aguas de estuario</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Valentina Upegui</t>
+          <t>Velia Vidal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1630,7 +1626,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Aguas de estuario</t>
+          <t>Diez lunas para una espera</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1643,20 +1639,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Diez lunas para una espera</t>
+          <t>Al faro</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Velia Vidal</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>Virginia Woolf</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Lumen</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Al faro</t>
+          <t>El cuarto de Jacob</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>El cuarto de Jacob</t>
+          <t>El lector común</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1690,7 +1690,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>El lector común</t>
+          <t>Fin de viaje</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Fin de viaje</t>
+          <t>Los años</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1724,7 +1724,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Los años</t>
+          <t>Momentos de vida</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Momentos de vida</t>
+          <t>Noche y día</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Noche y día</t>
+          <t>Tres guineas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tres guineas</t>
+          <t>Una habitación propia</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1783,21 +1783,17 @@
           <t>Virginia Woolf</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Lumen</t>
-        </is>
-      </c>
+      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Una habitación propia</t>
+          <t>La casa de las bellas durmientes</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Virginia Woolf</t>
+          <t>Yasunari Kawabata</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1805,7 +1801,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>La casa de las bellas durmientes</t>
+          <t>Mil grullas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1814,19 +1810,6 @@
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Mil grullas</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Yasunari Kawabata</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1811,6 +1811,23 @@
       </c>
       <c r="C103" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momentos estelares de la humanidad </t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Stefan Zweig</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Alma</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,6 +1828,23 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>To kill a mockingbird</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Harper Lee</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Harper Collins</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1845,6 +1845,23 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Daniel Cristancho</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Angosta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1831,32 +1831,15 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>To kill a mockingbird</t>
+          <t>Cartago</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Harper Lee</t>
+          <t>Daniel Cristancho</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
-        <is>
-          <t>Harper Collins</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Cartago</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Daniel Cristancho</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
         <is>
           <t>Angosta</t>
         </is>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,23 +1828,6 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Cartago</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Daniel Cristancho</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Angosta</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,17 +702,19 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>La aventura de Miguel Littín clandestino en Chile</t>
-        </is>
+      <c r="A22" t="n">
+        <v>1984</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gabriel García Márquez</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Debolsillo Edición Especial en Tapa Dura</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -725,34 +727,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Debolsillo Edición Especial en Tapa Dura</t>
+          <t>Alma</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>1984</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>El jardín de los Finzi Contini</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>George Orwell</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Alma</t>
-        </is>
-      </c>
+          <t>Giorgio Bassani</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>El jardín de los Finzi Contini</t>
+          <t>Sobre la violencia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Giorgio Bassani</t>
+          <t>Hannah Arendt</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -760,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sobre la violencia</t>
+          <t>La M de las moscas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hannah Arendt</t>
+          <t>Helena Araújo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -773,12 +773,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>La M de las moscas</t>
+          <t>Afrodita</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Helena Araújo</t>
+          <t>Isabel Allende</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -786,7 +786,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Afrodita</t>
+          <t xml:space="preserve">Amor </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amor </t>
+          <t>Cuentos de Eva Luna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -812,7 +812,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cuentos de Eva Luna</t>
+          <t>El juego de Ripper</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -825,7 +825,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>El juego de Ripper</t>
+          <t>El plan infinito</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>El plan infinito</t>
+          <t>El viento conoce mi nombre</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>El viento conoce mi nombre</t>
+          <t>El Zorro: comienza la leyenda</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>El Zorro: comienza la leyenda</t>
+          <t>Inés del alma mía</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Inés del alma mía</t>
+          <t>La gorda de porcelana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>La gorda de porcelana</t>
+          <t>Largo pétalo de mar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Largo pétalo de mar</t>
+          <t>Los amantes del Guggenheim</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Los amantes del Guggenheim</t>
+          <t>Mi país inventado</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mi país inventado</t>
+          <t>Mujeres del alma mía</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -942,7 +942,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mujeres del alma mía</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>El señor de los anillos</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Isabel Allende</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -968,12 +968,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>El señor de los anillos</t>
+          <t>Juvenilia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Jane Austen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -981,12 +981,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Juvenilia</t>
+          <t>El principio del mundo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jane Austen</t>
+          <t>Jeremías Gamboa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -994,12 +994,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>El principio del mundo</t>
+          <t>Los viejos marineros</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jeremías Gamboa</t>
+          <t>Jorge Amador</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1007,25 +1007,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Los viejos marineros</t>
+          <t>El Aleph</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jorge Amador</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Jorge Luis Borges</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Debolsillo Edición Especial en Tapa Dura</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>El Aleph</t>
+          <t>Ensayo sobre la ceguera</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jorge Luis Borges</t>
+          <t>José Saramago</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1037,29 +1041,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ensayo sobre la ceguera</t>
+          <t>Tú no matarás</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>José Saramago</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Debolsillo Edición Especial en Tapa Dura</t>
-        </is>
-      </c>
+          <t>Julia Navarro</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tú no matarás</t>
+          <t>Pan piedra</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Julia Navarro</t>
+          <t>Laura Andrea Garzón</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1067,12 +1067,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pan piedra</t>
+          <t>Delirio</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Laura Andrea Garzón</t>
+          <t>Laura Restrepo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Delirio</t>
+          <t>Los Divinos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1093,12 +1093,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Los Divinos</t>
+          <t>Una noche en el paraíso</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Laura Restrepo</t>
+          <t>Lucía Berlín</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1106,12 +1106,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Una noche en el paraíso</t>
+          <t>Las amazonas: mito e historia</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lucía Berlín</t>
+          <t>Lyn Webster Wild</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1119,12 +1119,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Las amazonas: mito e historia</t>
+          <t>Chambacú, corral de negros</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lyn Webster Wild</t>
+          <t>Manuel Zapata Olivella</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Chambacú, corral de negros</t>
+          <t>Changó, el gran putas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Changó, el gran putas</t>
+          <t>En Chimá nace un santo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1158,12 +1158,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>En Chimá nace un santo</t>
+          <t>El sonido de las olas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Manuel Zapata Olivella</t>
+          <t>Margarita García Robayo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>El sonido de las olas</t>
+          <t>Primera persona</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1184,12 +1184,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Primera persona</t>
+          <t>Al otro lado del Mar</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Margarita García Robayo</t>
+          <t>María Cristina Restrepo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1197,12 +1197,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Al otro lado del Mar</t>
+          <t>Lais</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>María Cristina Restrepo</t>
+          <t>María de Francia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1210,12 +1210,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Lais</t>
+          <t>Cartas a un joven sicólogo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>María de Francia</t>
+          <t>María Dolores Avia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1223,12 +1223,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cartas a un joven sicólogo</t>
+          <t>Los nombres que olvidamos</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>María Dolores Avia</t>
+          <t>María F. Fitzgerald</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1236,12 +1236,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Los nombres que olvidamos</t>
+          <t>Solo un poco aquí</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>María F. Fitzgerald</t>
+          <t>María Ospina Pizano</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1249,12 +1249,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solo un poco aquí</t>
+          <t>Este es el mar</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>María Ospina Pizano</t>
+          <t>Mariana Enriquez</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1262,12 +1262,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Este es el mar</t>
+          <t>Niñapájaroglaciar</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mariana Enriquez</t>
+          <t>Mariana Matija</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1275,12 +1275,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Niñapájaroglaciar</t>
+          <t>Mañana no te presentes</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mariana Matija</t>
+          <t>Marta Orrantia</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1288,12 +1288,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mañana no te presentes</t>
+          <t>Cuentos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Marta Orrantia</t>
+          <t>Marvel Moreno</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cuentos</t>
+          <t>En diciembre llegaban las garzas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1314,12 +1314,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>En diciembre llegaban las garzas</t>
+          <t>La casa de la belleza</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marvel Moreno</t>
+          <t>Melba Escobar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1327,12 +1327,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>La casa de la belleza</t>
+          <t>Reinventar el amor</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Melba Escobar</t>
+          <t>Mona Chollet</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1340,12 +1340,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Reinventar el amor</t>
+          <t>El enigma del amuleto</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mona Chollet</t>
+          <t>Mónica Acebedo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1353,12 +1353,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>El enigma del amuleto</t>
+          <t>Los errantes</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mónica Acebedo</t>
+          <t>Olga Tokarczuk</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1366,12 +1366,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Los errantes</t>
+          <t>La mujer del pelo rojo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Olga Tokarczuk</t>
+          <t>Orhan Pamuk</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1379,12 +1379,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>La mujer del pelo rojo</t>
+          <t>Lo que no tiene nombre</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Orhan Pamuk</t>
+          <t>Piedad Bonnet</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1392,12 +1392,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lo que no tiene nombre</t>
+          <t>Diccionario</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Piedad Bonnet</t>
+          <t>RAE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1405,12 +1405,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Diccionario</t>
+          <t>Horizontes para la paz</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RAE</t>
+          <t>Rafael Pardo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1418,12 +1418,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Horizontes para la paz</t>
+          <t>Lola Vendetta: Katanazo al amor romántico</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rafael Pardo</t>
+          <t>Raquel Riba Rossy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1431,12 +1431,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lola Vendetta: Katanazo al amor romántico</t>
+          <t>Nombres y animales</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Raquel Riba Rossy</t>
+          <t>Rita Indiana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1444,12 +1444,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Nombres y animales</t>
+          <t>El peso del corazón</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rita Indiana</t>
+          <t>Rosa Montero</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1457,7 +1457,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>El peso del corazón</t>
+          <t>La ridícula idea de no volverte a ver</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1470,12 +1470,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>La ridícula idea de no volverte a ver</t>
+          <t>El crisantemo y la espada</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rosa Montero</t>
+          <t>Ruth Benedict</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1483,12 +1483,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>El crisantemo y la espada</t>
+          <t>Pájaros en la Boca</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ruth Benedict</t>
+          <t>Samanta Schweblin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Pájaros en la Boca</t>
+          <t>La dependienta</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Samanta Schweblin</t>
+          <t>Sayaka Murata</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1509,12 +1509,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>La dependienta</t>
+          <t>Nada que decir</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sayaka Murata</t>
+          <t>Silvia Hidalgo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1522,12 +1522,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Nada que decir</t>
+          <t>La campana de cristal</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Silvia Hidalgo</t>
+          <t>Silvia Plath</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1535,12 +1535,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>La campana de cristal</t>
+          <t>Cauce y río</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Silvia Plath</t>
+          <t>Silvia Rivera Cusicanqui</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1548,12 +1548,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cauce y río</t>
+          <t>Emily Dickinson y lo incompleto</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Silvia Rivera Cusicanqui</t>
+          <t>Tania Ganitsky</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1561,12 +1561,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Emily Dickinson y lo incompleto</t>
+          <t>The once and future king</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tania Ganitsky</t>
+          <t>TH White</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1574,12 +1574,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>The once and future king</t>
+          <t>Budismo para principiantes</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TH White</t>
+          <t>Thubten Chodron</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1587,12 +1587,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Budismo para principiantes</t>
+          <t>Cuántas veces nunca más</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Thubten Chodron</t>
+          <t>Valentina Upegui</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1600,12 +1600,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cuántas veces nunca más</t>
+          <t>Aguas de estuario</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Valentina Upegui</t>
+          <t>Velia Vidal</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1613,7 +1613,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Aguas de estuario</t>
+          <t>Diez lunas para una espera</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1626,20 +1626,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Diez lunas para una espera</t>
+          <t>Al faro</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Velia Vidal</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>Virginia Woolf</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Lumen</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Al faro</t>
+          <t>El cuarto de Jacob</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1656,7 +1660,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>El cuarto de Jacob</t>
+          <t>El lector común</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1673,7 +1677,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>El lector común</t>
+          <t>Fin de viaje</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1690,7 +1694,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Fin de viaje</t>
+          <t>Los años</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1707,7 +1711,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Los años</t>
+          <t>Momentos de vida</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1724,7 +1728,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Momentos de vida</t>
+          <t>Noche y día</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1741,7 +1745,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Noche y día</t>
+          <t>Tres guineas</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1758,7 +1762,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tres guineas</t>
+          <t>Una habitación propia</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1766,21 +1770,17 @@
           <t>Virginia Woolf</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Lumen</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Una habitación propia</t>
+          <t>La casa de las bellas durmientes</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Virginia Woolf</t>
+          <t>Yasunari Kawabata</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>La casa de las bellas durmientes</t>
+          <t>Mil grullas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1801,28 +1801,15 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Mil grullas</t>
+          <t xml:space="preserve">Momentos estelares de la humanidad </t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Yasunari Kawabata</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Momentos estelares de la humanidad </t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
           <t>Stefan Zweig</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Alma</t>
         </is>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,6 +1815,23 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de París 2/2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Victor Hugo</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Edelvives</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1832,6 +1832,15 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Orwell</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1841,6 +1841,24 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Orwell</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Orwell</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,34 +712,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Debolsillo Edición Especial en Tapa Dura</t>
+          <t>Alma</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>1984</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>El jardín de los Finzi Contini</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>George Orwell</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Alma</t>
-        </is>
-      </c>
+          <t>Giorgio Bassani</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>El jardín de los Finzi Contini</t>
+          <t>Sobre la violencia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Giorgio Bassani</t>
+          <t>Hannah Arendt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -747,12 +745,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sobre la violencia</t>
+          <t>La M de las moscas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hannah Arendt</t>
+          <t>Helena Araújo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -760,12 +758,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>La M de las moscas</t>
+          <t>Afrodita</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Helena Araújo</t>
+          <t>Isabel Allende</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -773,7 +771,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Afrodita</t>
+          <t xml:space="preserve">Amor </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -786,7 +784,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amor </t>
+          <t>Cuentos de Eva Luna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -799,7 +797,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cuentos de Eva Luna</t>
+          <t>El juego de Ripper</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -812,7 +810,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>El juego de Ripper</t>
+          <t>El plan infinito</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -825,7 +823,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>El plan infinito</t>
+          <t>El viento conoce mi nombre</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -838,7 +836,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>El viento conoce mi nombre</t>
+          <t>El Zorro: comienza la leyenda</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -851,7 +849,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>El Zorro: comienza la leyenda</t>
+          <t>Inés del alma mía</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -864,7 +862,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Inés del alma mía</t>
+          <t>La gorda de porcelana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -877,7 +875,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>La gorda de porcelana</t>
+          <t>Largo pétalo de mar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -890,7 +888,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Largo pétalo de mar</t>
+          <t>Los amantes del Guggenheim</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -903,7 +901,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Los amantes del Guggenheim</t>
+          <t>Mi país inventado</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -916,7 +914,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mi país inventado</t>
+          <t>Mujeres del alma mía</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -929,7 +927,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mujeres del alma mía</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -942,12 +940,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>El señor de los anillos</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Isabel Allende</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -955,12 +953,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>El señor de los anillos</t>
+          <t>Juvenilia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Jane Austen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -968,12 +966,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Juvenilia</t>
+          <t>El principio del mundo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jane Austen</t>
+          <t>Jeremías Gamboa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -981,12 +979,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>El principio del mundo</t>
+          <t>Los viejos marineros</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jeremías Gamboa</t>
+          <t>Jorge Amador</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -994,25 +992,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Los viejos marineros</t>
+          <t>El Aleph</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jorge Amador</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Jorge Luis Borges</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Debolsillo Edición Especial en Tapa Dura</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>El Aleph</t>
+          <t>Ensayo sobre la ceguera</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jorge Luis Borges</t>
+          <t>José Saramago</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1024,29 +1026,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ensayo sobre la ceguera</t>
+          <t>Tú no matarás</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>José Saramago</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Debolsillo Edición Especial en Tapa Dura</t>
-        </is>
-      </c>
+          <t>Julia Navarro</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tú no matarás</t>
+          <t>Pan piedra</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Julia Navarro</t>
+          <t>Laura Andrea Garzón</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1054,12 +1052,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pan piedra</t>
+          <t>Delirio</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Laura Andrea Garzón</t>
+          <t>Laura Restrepo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1067,7 +1065,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Delirio</t>
+          <t>Los Divinos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1080,12 +1078,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Los Divinos</t>
+          <t>Una noche en el paraíso</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Laura Restrepo</t>
+          <t>Lucía Berlín</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1093,12 +1091,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Una noche en el paraíso</t>
+          <t>Las amazonas: mito e historia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lucía Berlín</t>
+          <t>Lyn Webster Wild</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1106,12 +1104,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Las amazonas: mito e historia</t>
+          <t>Chambacú, corral de negros</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lyn Webster Wild</t>
+          <t>Manuel Zapata Olivella</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1119,7 +1117,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Chambacú, corral de negros</t>
+          <t>Changó, el gran putas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1132,7 +1130,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Changó, el gran putas</t>
+          <t>En Chimá nace un santo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1145,12 +1143,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>En Chimá nace un santo</t>
+          <t>El sonido de las olas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Manuel Zapata Olivella</t>
+          <t>Margarita García Robayo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1158,7 +1156,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>El sonido de las olas</t>
+          <t>Primera persona</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1171,12 +1169,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Primera persona</t>
+          <t>Al otro lado del Mar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Margarita García Robayo</t>
+          <t>María Cristina Restrepo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1184,12 +1182,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Al otro lado del Mar</t>
+          <t>Lais</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>María Cristina Restrepo</t>
+          <t>María de Francia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1197,12 +1195,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lais</t>
+          <t>Cartas a un joven sicólogo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>María de Francia</t>
+          <t>María Dolores Avia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1210,12 +1208,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cartas a un joven sicólogo</t>
+          <t>Los nombres que olvidamos</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>María Dolores Avia</t>
+          <t>María F. Fitzgerald</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1223,12 +1221,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Los nombres que olvidamos</t>
+          <t>Solo un poco aquí</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>María F. Fitzgerald</t>
+          <t>María Ospina Pizano</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1236,12 +1234,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solo un poco aquí</t>
+          <t>Este es el mar</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>María Ospina Pizano</t>
+          <t>Mariana Enriquez</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1249,12 +1247,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Este es el mar</t>
+          <t>Niñapájaroglaciar</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mariana Enriquez</t>
+          <t>Mariana Matija</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1262,12 +1260,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Niñapájaroglaciar</t>
+          <t>Mañana no te presentes</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mariana Matija</t>
+          <t>Marta Orrantia</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1275,12 +1273,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mañana no te presentes</t>
+          <t>Cuentos</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Marta Orrantia</t>
+          <t>Marvel Moreno</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1288,7 +1286,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cuentos</t>
+          <t>En diciembre llegaban las garzas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1301,12 +1299,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>En diciembre llegaban las garzas</t>
+          <t>La casa de la belleza</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Marvel Moreno</t>
+          <t>Melba Escobar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1314,12 +1312,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>La casa de la belleza</t>
+          <t>Reinventar el amor</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Melba Escobar</t>
+          <t>Mona Chollet</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1327,12 +1325,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Reinventar el amor</t>
+          <t>El enigma del amuleto</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mona Chollet</t>
+          <t>Mónica Acebedo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1340,12 +1338,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>El enigma del amuleto</t>
+          <t>Los errantes</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mónica Acebedo</t>
+          <t>Olga Tokarczuk</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1353,12 +1351,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Los errantes</t>
+          <t>La mujer del pelo rojo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Olga Tokarczuk</t>
+          <t>Orhan Pamuk</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1366,12 +1364,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>La mujer del pelo rojo</t>
+          <t>Lo que no tiene nombre</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Orhan Pamuk</t>
+          <t>Piedad Bonnet</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1379,12 +1377,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lo que no tiene nombre</t>
+          <t>Diccionario</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Piedad Bonnet</t>
+          <t>RAE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1392,12 +1390,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Diccionario</t>
+          <t>Horizontes para la paz</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RAE</t>
+          <t>Rafael Pardo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1405,12 +1403,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Horizontes para la paz</t>
+          <t>Lola Vendetta: Katanazo al amor romántico</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rafael Pardo</t>
+          <t>Raquel Riba Rossy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1418,12 +1416,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lola Vendetta: Katanazo al amor romántico</t>
+          <t>Nombres y animales</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Raquel Riba Rossy</t>
+          <t>Rita Indiana</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1431,12 +1429,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nombres y animales</t>
+          <t>El peso del corazón</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Rita Indiana</t>
+          <t>Rosa Montero</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1444,7 +1442,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>El peso del corazón</t>
+          <t>La ridícula idea de no volverte a ver</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1457,12 +1455,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>La ridícula idea de no volverte a ver</t>
+          <t>El crisantemo y la espada</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rosa Montero</t>
+          <t>Ruth Benedict</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1470,12 +1468,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>El crisantemo y la espada</t>
+          <t>Pájaros en la Boca</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ruth Benedict</t>
+          <t>Samanta Schweblin</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1483,12 +1481,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Pájaros en la Boca</t>
+          <t>La dependienta</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Samanta Schweblin</t>
+          <t>Sayaka Murata</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1496,12 +1494,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>La dependienta</t>
+          <t>Nada que decir</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sayaka Murata</t>
+          <t>Silvia Hidalgo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1509,12 +1507,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Nada que decir</t>
+          <t>La campana de cristal</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Silvia Hidalgo</t>
+          <t>Silvia Plath</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1522,12 +1520,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>La campana de cristal</t>
+          <t>Cauce y río</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Silvia Plath</t>
+          <t>Silvia Rivera Cusicanqui</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1535,12 +1533,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cauce y río</t>
+          <t>Emily Dickinson y lo incompleto</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Silvia Rivera Cusicanqui</t>
+          <t>Tania Ganitsky</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1548,12 +1546,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Emily Dickinson y lo incompleto</t>
+          <t>The once and future king</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tania Ganitsky</t>
+          <t>TH White</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1561,12 +1559,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>The once and future king</t>
+          <t>Budismo para principiantes</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TH White</t>
+          <t>Thubten Chodron</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1574,12 +1572,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Budismo para principiantes</t>
+          <t>Cuántas veces nunca más</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Thubten Chodron</t>
+          <t>Valentina Upegui</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1587,12 +1585,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cuántas veces nunca más</t>
+          <t>Aguas de estuario</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Valentina Upegui</t>
+          <t>Velia Vidal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1600,7 +1598,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Aguas de estuario</t>
+          <t>Diez lunas para una espera</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1613,20 +1611,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Diez lunas para una espera</t>
+          <t>Al faro</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Velia Vidal</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>Virginia Woolf</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Lumen</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Al faro</t>
+          <t>El cuarto de Jacob</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1643,7 +1645,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>El cuarto de Jacob</t>
+          <t>El lector común</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1660,7 +1662,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>El lector común</t>
+          <t>Fin de viaje</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1677,7 +1679,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fin de viaje</t>
+          <t>Los años</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1694,7 +1696,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Los años</t>
+          <t>Momentos de vida</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1711,7 +1713,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Momentos de vida</t>
+          <t>Noche y día</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1728,7 +1730,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Noche y día</t>
+          <t>Tres guineas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1745,7 +1747,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tres guineas</t>
+          <t>Una habitación propia</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1753,21 +1755,17 @@
           <t>Virginia Woolf</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Lumen</t>
-        </is>
-      </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Una habitación propia</t>
+          <t>La casa de las bellas durmientes</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Virginia Woolf</t>
+          <t>Yasunari Kawabata</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1775,7 +1773,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>La casa de las bellas durmientes</t>
+          <t>Mil grullas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1788,49 +1786,45 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mil grullas</t>
+          <t xml:space="preserve">Momentos estelares de la humanidad </t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Yasunari Kawabata</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>Stefan Zweig</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Alma</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Momentos estelares de la humanidad </t>
+          <t>Nuestra Señora de París 2/2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Stefan Zweig</t>
+          <t>Victor Hugo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Alma</t>
+          <t>Edelvives</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Nuestra Señora de París 2/2</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Victor Hugo</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Edelvives</t>
-        </is>
-      </c>
+          <t>Orwell</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1849,15 +1843,6 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Orwell</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1835,15 +1835,6 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Orwell</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1826,15 +1826,6 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Orwell</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nini/Wishlist.xlsx
+++ b/data/nini/Wishlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1817,15 +1817,6 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Orwell</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
